--- a/data/District.xlsx
+++ b/data/District.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adriel\Documents\Website Projects\Portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7EFA9B-90B9-4F76-8FCF-CAA85C0627BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFFF197-2DC3-4C53-9F9F-A0215A242A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D9DBF409-B6A8-4624-B9A2-2D76F3C06551}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D9DBF409-B6A8-4624-B9A2-2D76F3C06551}"/>
   </bookViews>
   <sheets>
     <sheet name="CAVITE PER DISTRICT" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -292,21 +292,29 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Adriel" refreshedDate="46272.584068055556" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="437" xr:uid="{F823ADB1-8768-4087-A19F-342F5F492B3A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Adriel" refreshedDate="46277.958794675927" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="437" xr:uid="{F823ADB1-8768-4087-A19F-342F5F492B3A}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="District" numFmtId="0">
-      <sharedItems count="8">
-        <s v="1ST DISTRICT"/>
-        <s v="2ND DISTRICT"/>
-        <s v="3RD DISTRICT"/>
-        <s v="4TH DISTRICT"/>
-        <s v="5TH DISTRICT"/>
-        <s v="6TH DISTRICT"/>
-        <s v="7TH DISTRICT"/>
-        <s v="8TH DISTRICT"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="8" count="16">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <s v="1ST DISTRICT" u="1"/>
+        <s v="2ND DISTRICT" u="1"/>
+        <s v="3RD DISTRICT" u="1"/>
+        <s v="4TH DISTRICT" u="1"/>
+        <s v="5TH DISTRICT" u="1"/>
+        <s v="6TH DISTRICT" u="1"/>
+        <s v="7TH DISTRICT" u="1"/>
+        <s v="8TH DISTRICT" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="City" numFmtId="0">
@@ -360,83 +368,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Premium" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2153" count="75">
-        <n v="503"/>
-        <n v="0"/>
-        <n v="12"/>
-        <n v="390"/>
-        <n v="51"/>
-        <n v="37"/>
-        <n v="68"/>
-        <n v="20"/>
-        <n v="44"/>
-        <n v="176"/>
-        <n v="55"/>
-        <n v="7"/>
-        <n v="328"/>
-        <n v="362"/>
-        <n v="5"/>
-        <n v="34"/>
-        <n v="164"/>
-        <n v="785"/>
-        <n v="45"/>
-        <n v="347"/>
-        <n v="670"/>
-        <n v="3"/>
-        <n v="33"/>
-        <n v="308"/>
-        <n v="14"/>
-        <n v="59"/>
-        <n v="1579"/>
-        <n v="185"/>
-        <n v="2153"/>
-        <n v="156"/>
-        <n v="18"/>
-        <n v="2"/>
-        <n v="57"/>
-        <n v="1104"/>
-        <n v="116"/>
-        <n v="267"/>
-        <n v="221"/>
-        <n v="1496"/>
-        <n v="241"/>
-        <n v="8"/>
-        <n v="15"/>
-        <n v="13"/>
-        <n v="858"/>
-        <n v="138"/>
-        <n v="499"/>
-        <n v="403"/>
-        <n v="6"/>
-        <n v="10"/>
-        <n v="310"/>
-        <n v="31"/>
-        <n v="183"/>
-        <n v="173"/>
-        <n v="361"/>
-        <n v="76"/>
-        <n v="1"/>
-        <n v="980"/>
-        <n v="25"/>
-        <n v="348"/>
-        <n v="111"/>
-        <n v="1224"/>
-        <n v="1052"/>
-        <n v="234"/>
-        <n v="60"/>
-        <n v="270"/>
-        <n v="519"/>
-        <n v="737"/>
-        <n v="100"/>
-        <n v="1013"/>
-        <n v="346"/>
-        <n v="679"/>
-        <n v="279"/>
-        <n v="4"/>
-        <n v="421"/>
-        <n v="964"/>
-        <n v="86"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2153"/>
     </cacheField>
     <cacheField name="Bronze" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1032"/>
@@ -448,10 +380,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="84"/>
     </cacheField>
     <cacheField name="Platinum" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="30"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="43"/>
     </cacheField>
     <cacheField name="Diamond" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="55"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -468,7 +400,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
+    <n v="503"/>
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
@@ -479,7 +411,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -490,18 +422,18 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <x v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="12"/>
     <n v="0"/>
     <n v="0"/>
@@ -512,7 +444,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <x v="3"/>
+    <n v="390"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -523,7 +455,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -534,7 +466,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <x v="4"/>
+    <n v="51"/>
     <n v="163"/>
     <n v="0"/>
     <n v="0"/>
@@ -545,18 +477,18 @@
     <x v="0"/>
     <x v="0"/>
     <x v="7"/>
-    <x v="5"/>
+    <n v="37"/>
     <n v="20"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="24"/>
   </r>
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="6"/>
+    <n v="68"/>
     <n v="79"/>
     <n v="7"/>
     <n v="2"/>
@@ -567,7 +499,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -578,7 +510,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -589,7 +521,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -600,7 +532,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -611,7 +543,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -622,7 +554,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
@@ -633,7 +565,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="187"/>
     <n v="0"/>
     <n v="0"/>
@@ -644,7 +576,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="318"/>
     <n v="0"/>
     <n v="1"/>
@@ -655,7 +587,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="17"/>
-    <x v="7"/>
+    <n v="20"/>
     <n v="71"/>
     <n v="7"/>
     <n v="3"/>
@@ -666,7 +598,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="18"/>
-    <x v="8"/>
+    <n v="44"/>
     <n v="26"/>
     <n v="16"/>
     <n v="6"/>
@@ -677,7 +609,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
-    <x v="9"/>
+    <n v="176"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -688,7 +620,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -699,7 +631,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -710,7 +642,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -721,7 +653,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -732,7 +664,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -743,18 +675,18 @@
     <x v="0"/>
     <x v="1"/>
     <x v="6"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
+    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -765,7 +697,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -776,18 +708,18 @@
     <x v="0"/>
     <x v="1"/>
     <x v="9"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -798,7 +730,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -809,7 +741,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -820,7 +752,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -831,7 +763,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -842,7 +774,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -853,7 +785,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -864,7 +796,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="31"/>
@@ -875,7 +807,7 @@
     <x v="0"/>
     <x v="1"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -886,7 +818,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -897,7 +829,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="6"/>
@@ -908,7 +840,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -919,7 +851,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -930,7 +862,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -941,18 +873,18 @@
     <x v="0"/>
     <x v="2"/>
     <x v="5"/>
-    <x v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="55"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -963,7 +895,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -974,7 +906,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="8"/>
-    <x v="11"/>
+    <n v="7"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -985,7 +917,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -996,7 +928,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1007,7 +939,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1018,18 +950,18 @@
     <x v="0"/>
     <x v="2"/>
     <x v="12"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="43"/>
     <n v="0"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1040,7 +972,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1051,7 +983,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1062,7 +994,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1073,7 +1005,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1084,7 +1016,7 @@
     <x v="0"/>
     <x v="2"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1095,7 +1027,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="0"/>
-    <x v="12"/>
+    <n v="328"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1106,7 +1038,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1117,7 +1049,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="13"/>
+    <n v="362"/>
     <n v="7"/>
     <n v="0"/>
     <n v="0"/>
@@ -1128,7 +1060,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1139,7 +1071,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1150,7 +1082,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1161,7 +1093,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1172,7 +1104,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1183,7 +1115,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="8"/>
-    <x v="14"/>
+    <n v="5"/>
     <n v="38"/>
     <n v="98"/>
     <n v="35"/>
@@ -1194,7 +1126,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1205,7 +1137,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="10"/>
-    <x v="15"/>
+    <n v="34"/>
     <n v="43"/>
     <n v="0"/>
     <n v="5"/>
@@ -1216,7 +1148,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1227,7 +1159,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1238,7 +1170,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1249,7 +1181,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1260,7 +1192,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1271,7 +1203,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="248"/>
     <n v="0"/>
     <n v="0"/>
@@ -1282,7 +1214,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1293,7 +1225,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1304,7 +1236,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="0"/>
-    <x v="16"/>
+    <n v="164"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -1315,7 +1247,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="1"/>
-    <x v="17"/>
+    <n v="785"/>
     <n v="52"/>
     <n v="0"/>
     <n v="0"/>
@@ -1326,7 +1258,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="2"/>
-    <x v="18"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1337,7 +1269,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="3"/>
-    <x v="19"/>
+    <n v="347"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1348,7 +1280,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="4"/>
-    <x v="20"/>
+    <n v="670"/>
     <n v="9"/>
     <n v="0"/>
     <n v="0"/>
@@ -1359,7 +1291,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="5"/>
-    <x v="21"/>
+    <n v="3"/>
     <n v="84"/>
     <n v="0"/>
     <n v="0"/>
@@ -1370,7 +1302,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="6"/>
-    <x v="22"/>
+    <n v="33"/>
     <n v="11"/>
     <n v="0"/>
     <n v="3"/>
@@ -1381,7 +1313,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="7"/>
-    <x v="23"/>
+    <n v="308"/>
     <n v="163"/>
     <n v="1"/>
     <n v="0"/>
@@ -1392,7 +1324,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="8"/>
-    <x v="24"/>
+    <n v="14"/>
     <n v="0"/>
     <n v="13"/>
     <n v="9"/>
@@ -1403,7 +1335,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1414,7 +1346,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="10"/>
-    <x v="25"/>
+    <n v="59"/>
     <n v="40"/>
     <n v="8"/>
     <n v="3"/>
@@ -1425,7 +1357,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="11"/>
-    <x v="24"/>
+    <n v="14"/>
     <n v="17"/>
     <n v="0"/>
     <n v="0"/>
@@ -1436,7 +1368,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1447,7 +1379,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="13"/>
-    <x v="14"/>
+    <n v="5"/>
     <n v="7"/>
     <n v="6"/>
     <n v="2"/>
@@ -1458,7 +1390,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1469,7 +1401,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="42"/>
     <n v="0"/>
     <n v="0"/>
@@ -1480,7 +1412,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="268"/>
     <n v="0"/>
     <n v="0"/>
@@ -1491,7 +1423,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -1502,7 +1434,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="7"/>
     <n v="0"/>
     <n v="0"/>
@@ -1513,18 +1445,18 @@
     <x v="2"/>
     <x v="5"/>
     <x v="0"/>
-    <x v="26"/>
+    <n v="1579"/>
     <n v="26"/>
     <n v="9"/>
     <n v="2"/>
     <n v="1"/>
-    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="2"/>
     <x v="5"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1535,7 +1467,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1546,7 +1478,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="3"/>
-    <x v="27"/>
+    <n v="185"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1557,7 +1489,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="4"/>
-    <x v="28"/>
+    <n v="2153"/>
     <n v="33"/>
     <n v="11"/>
     <n v="4"/>
@@ -1568,7 +1500,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="5"/>
-    <x v="29"/>
+    <n v="156"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1579,7 +1511,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1590,7 +1522,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1601,7 +1533,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="8"/>
-    <x v="30"/>
+    <n v="18"/>
     <n v="39"/>
     <n v="0"/>
     <n v="0"/>
@@ -1612,7 +1544,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="9"/>
-    <x v="31"/>
+    <n v="2"/>
     <n v="2"/>
     <n v="5"/>
     <n v="2"/>
@@ -1623,7 +1555,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="10"/>
-    <x v="32"/>
+    <n v="57"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -1634,7 +1566,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1645,7 +1577,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1656,7 +1588,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="13"/>
-    <x v="31"/>
+    <n v="2"/>
     <n v="2"/>
     <n v="6"/>
     <n v="0"/>
@@ -1667,7 +1599,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="2"/>
     <n v="5"/>
     <n v="3"/>
@@ -1678,7 +1610,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -1689,7 +1621,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="107"/>
     <n v="0"/>
     <n v="0"/>
@@ -1700,7 +1632,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -1711,7 +1643,7 @@
     <x v="2"/>
     <x v="5"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1722,7 +1654,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="0"/>
-    <x v="33"/>
+    <n v="1104"/>
     <n v="101"/>
     <n v="8"/>
     <n v="4"/>
@@ -1733,7 +1665,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="1"/>
-    <x v="34"/>
+    <n v="116"/>
     <n v="22"/>
     <n v="0"/>
     <n v="0"/>
@@ -1744,7 +1676,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="2"/>
-    <x v="35"/>
+    <n v="267"/>
     <n v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -1755,7 +1687,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="31"/>
+    <n v="2"/>
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
@@ -1766,7 +1698,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="4"/>
-    <x v="36"/>
+    <n v="221"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1777,7 +1709,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="5"/>
-    <x v="37"/>
+    <n v="1496"/>
     <n v="9"/>
     <n v="0"/>
     <n v="0"/>
@@ -1788,7 +1720,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1799,18 +1731,18 @@
     <x v="3"/>
     <x v="6"/>
     <x v="7"/>
-    <x v="38"/>
+    <n v="241"/>
     <n v="862"/>
     <n v="14"/>
     <n v="4"/>
     <n v="1"/>
-    <n v="0"/>
+    <n v="13"/>
   </r>
   <r>
     <x v="3"/>
     <x v="6"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="187"/>
     <n v="20"/>
     <n v="48"/>
@@ -1821,18 +1753,18 @@
     <x v="3"/>
     <x v="6"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1"/>
     <n v="1"/>
     <n v="3"/>
-    <n v="0"/>
+    <n v="32"/>
     <n v="1"/>
   </r>
   <r>
     <x v="3"/>
     <x v="6"/>
     <x v="10"/>
-    <x v="39"/>
+    <n v="8"/>
     <n v="206"/>
     <n v="76"/>
     <n v="9"/>
@@ -1843,7 +1775,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1854,7 +1786,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1865,7 +1797,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="13"/>
-    <x v="31"/>
+    <n v="2"/>
     <n v="0"/>
     <n v="2"/>
     <n v="3"/>
@@ -1876,7 +1808,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="2"/>
     <n v="1"/>
     <n v="2"/>
@@ -1887,7 +1819,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="341"/>
     <n v="0"/>
     <n v="0"/>
@@ -1898,7 +1830,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1032"/>
     <n v="0"/>
     <n v="10"/>
@@ -1909,7 +1841,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="17"/>
-    <x v="40"/>
+    <n v="15"/>
     <n v="91"/>
     <n v="8"/>
     <n v="12"/>
@@ -1920,7 +1852,7 @@
     <x v="3"/>
     <x v="6"/>
     <x v="18"/>
-    <x v="41"/>
+    <n v="13"/>
     <n v="60"/>
     <n v="4"/>
     <n v="4"/>
@@ -1931,7 +1863,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="0"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1942,7 +1874,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1953,7 +1885,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1964,18 +1896,18 @@
     <x v="4"/>
     <x v="7"/>
     <x v="3"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="4"/>
     <x v="7"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1986,7 +1918,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -1997,7 +1929,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2008,7 +1940,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2019,7 +1951,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="111"/>
     <n v="0"/>
     <n v="0"/>
@@ -2030,7 +1962,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2041,7 +1973,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2052,7 +1984,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="27"/>
     <n v="0"/>
     <n v="0"/>
@@ -2063,7 +1995,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="489"/>
     <n v="195"/>
     <n v="0"/>
@@ -2074,7 +2006,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2085,7 +2017,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2096,7 +2028,7 @@
     <x v="4"/>
     <x v="7"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="129"/>
     <n v="0"/>
     <n v="0"/>
@@ -2107,29 +2039,29 @@
     <x v="4"/>
     <x v="7"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="76"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="7"/>
     <x v="17"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
   </r>
   <r>
     <x v="4"/>
     <x v="7"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2140,7 +2072,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="0"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2151,7 +2083,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2162,7 +2094,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -2173,7 +2105,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2184,7 +2116,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2195,7 +2127,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="9"/>
     <n v="0"/>
     <n v="0"/>
@@ -2206,7 +2138,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -2217,18 +2149,18 @@
     <x v="4"/>
     <x v="8"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="90"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="4"/>
     <x v="8"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="4"/>
     <n v="12"/>
@@ -2239,7 +2171,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2250,7 +2182,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2261,7 +2193,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="51"/>
     <n v="84"/>
@@ -2272,7 +2204,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2283,7 +2215,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2294,7 +2226,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2305,18 +2237,18 @@
     <x v="4"/>
     <x v="8"/>
     <x v="15"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6"/>
   </r>
   <r>
     <x v="4"/>
     <x v="8"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2327,7 +2259,7 @@
     <x v="4"/>
     <x v="8"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -2338,18 +2270,18 @@
     <x v="4"/>
     <x v="8"/>
     <x v="18"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="9"/>
     <x v="0"/>
-    <x v="42"/>
+    <n v="858"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -2360,7 +2292,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="1"/>
-    <x v="43"/>
+    <n v="138"/>
     <n v="19"/>
     <n v="0"/>
     <n v="0"/>
@@ -2371,18 +2303,18 @@
     <x v="4"/>
     <x v="9"/>
     <x v="2"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="4"/>
     <x v="9"/>
     <x v="3"/>
-    <x v="44"/>
+    <n v="499"/>
     <n v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -2393,7 +2325,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -2404,7 +2336,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="4"/>
+    <n v="51"/>
     <n v="51"/>
     <n v="0"/>
     <n v="0"/>
@@ -2415,29 +2347,29 @@
     <x v="4"/>
     <x v="9"/>
     <x v="6"/>
-    <x v="21"/>
+    <n v="3"/>
     <n v="19"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="6"/>
     <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="9"/>
     <x v="7"/>
-    <x v="45"/>
+    <n v="403"/>
     <n v="6"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="4"/>
     <x v="9"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="44"/>
     <n v="2"/>
     <n v="0"/>
@@ -2448,7 +2380,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2459,7 +2391,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="10"/>
-    <x v="14"/>
+    <n v="5"/>
     <n v="24"/>
     <n v="52"/>
     <n v="0"/>
@@ -2470,7 +2402,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2481,7 +2413,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2492,18 +2424,18 @@
     <x v="4"/>
     <x v="9"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1"/>
     <n v="0"/>
     <n v="2"/>
-    <n v="0"/>
+    <n v="6"/>
     <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="9"/>
     <x v="14"/>
-    <x v="46"/>
+    <n v="6"/>
     <n v="16"/>
     <n v="12"/>
     <n v="0"/>
@@ -2514,7 +2446,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="567"/>
     <n v="0"/>
     <n v="0"/>
@@ -2525,7 +2457,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="205"/>
     <n v="0"/>
     <n v="0"/>
@@ -2536,7 +2468,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="17"/>
-    <x v="14"/>
+    <n v="5"/>
     <n v="104"/>
     <n v="43"/>
     <n v="0"/>
@@ -2547,7 +2479,7 @@
     <x v="4"/>
     <x v="9"/>
     <x v="18"/>
-    <x v="47"/>
+    <n v="10"/>
     <n v="64"/>
     <n v="10"/>
     <n v="4"/>
@@ -2558,7 +2490,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="0"/>
-    <x v="48"/>
+    <n v="310"/>
     <n v="2"/>
     <n v="0"/>
     <n v="4"/>
@@ -2569,7 +2501,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="1"/>
-    <x v="49"/>
+    <n v="31"/>
     <n v="8"/>
     <n v="0"/>
     <n v="0"/>
@@ -2580,7 +2512,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="2"/>
-    <x v="50"/>
+    <n v="183"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -2591,7 +2523,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2602,7 +2534,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="4"/>
-    <x v="51"/>
+    <n v="173"/>
     <n v="5"/>
     <n v="0"/>
     <n v="0"/>
@@ -2613,7 +2545,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2624,7 +2556,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="6"/>
-    <x v="52"/>
+    <n v="361"/>
     <n v="4"/>
     <n v="0"/>
     <n v="0"/>
@@ -2635,7 +2567,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2646,7 +2578,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="3"/>
     <n v="5"/>
     <n v="37"/>
@@ -2657,7 +2589,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2668,7 +2600,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="53"/>
+    <n v="76"/>
     <n v="10"/>
     <n v="4"/>
     <n v="4"/>
@@ -2679,7 +2611,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="8"/>
     <n v="0"/>
     <n v="0"/>
@@ -2690,7 +2622,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2701,7 +2633,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="13"/>
-    <x v="54"/>
+    <n v="1"/>
     <n v="16"/>
     <n v="5"/>
     <n v="2"/>
@@ -2712,18 +2644,18 @@
     <x v="5"/>
     <x v="10"/>
     <x v="14"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
     <n v="0"/>
   </r>
   <r>
     <x v="5"/>
     <x v="10"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="24"/>
     <n v="0"/>
     <n v="0"/>
@@ -2734,7 +2666,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="353"/>
     <n v="0"/>
     <n v="0"/>
@@ -2745,7 +2677,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2756,7 +2688,7 @@
     <x v="5"/>
     <x v="10"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2767,7 +2699,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="0"/>
-    <x v="54"/>
+    <n v="1"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2778,18 +2710,18 @@
     <x v="6"/>
     <x v="11"/>
     <x v="1"/>
-    <x v="6"/>
+    <n v="68"/>
     <n v="11"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="6"/>
     <x v="11"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2800,7 +2732,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2811,7 +2743,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2822,7 +2754,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2833,7 +2765,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2844,7 +2776,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2855,7 +2787,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="4"/>
     <n v="4"/>
@@ -2866,7 +2798,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2877,7 +2809,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2888,7 +2820,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2899,7 +2831,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2910,18 +2842,18 @@
     <x v="6"/>
     <x v="11"/>
     <x v="13"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="6"/>
     <x v="11"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2932,7 +2864,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2943,7 +2875,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2954,7 +2886,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2965,7 +2897,7 @@
     <x v="6"/>
     <x v="11"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2976,7 +2908,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="0"/>
-    <x v="55"/>
+    <n v="980"/>
     <n v="62"/>
     <n v="2"/>
     <n v="0"/>
@@ -2987,7 +2919,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -2998,7 +2930,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -3009,7 +2941,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3020,18 +2952,18 @@
     <x v="6"/>
     <x v="12"/>
     <x v="4"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6"/>
     <n v="0"/>
   </r>
   <r>
     <x v="6"/>
     <x v="12"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3042,7 +2974,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="6"/>
-    <x v="56"/>
+    <n v="25"/>
     <n v="3"/>
     <n v="0"/>
     <n v="1"/>
@@ -3053,7 +2985,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3064,7 +2996,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3075,7 +3007,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3086,7 +3018,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3097,7 +3029,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3108,7 +3040,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3119,7 +3051,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3130,7 +3062,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3141,7 +3073,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3152,7 +3084,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3163,7 +3095,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3174,7 +3106,7 @@
     <x v="6"/>
     <x v="12"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3185,7 +3117,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="0"/>
-    <x v="57"/>
+    <n v="348"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3196,7 +3128,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3207,7 +3139,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="2"/>
-    <x v="58"/>
+    <n v="111"/>
     <n v="11"/>
     <n v="4"/>
     <n v="1"/>
@@ -3218,7 +3150,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="3"/>
-    <x v="59"/>
+    <n v="1224"/>
     <n v="18"/>
     <n v="0"/>
     <n v="0"/>
@@ -3229,7 +3161,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="4"/>
-    <x v="60"/>
+    <n v="1052"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -3240,7 +3172,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3251,18 +3183,18 @@
     <x v="6"/>
     <x v="13"/>
     <x v="6"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="6"/>
     <x v="13"/>
     <x v="7"/>
-    <x v="61"/>
+    <n v="234"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3273,7 +3205,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="8"/>
-    <x v="21"/>
+    <n v="3"/>
     <n v="9"/>
     <n v="0"/>
     <n v="2"/>
@@ -3284,7 +3216,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3295,7 +3227,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="10"/>
-    <x v="62"/>
+    <n v="60"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3306,7 +3238,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3317,7 +3249,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3328,7 +3260,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="13"/>
-    <x v="54"/>
+    <n v="1"/>
     <n v="3"/>
     <n v="1"/>
     <n v="1"/>
@@ -3339,7 +3271,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3350,7 +3282,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3361,7 +3293,7 @@
     <x v="6"/>
     <x v="13"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="33"/>
     <n v="0"/>
     <n v="0"/>
@@ -3372,18 +3304,18 @@
     <x v="6"/>
     <x v="13"/>
     <x v="17"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="32"/>
   </r>
   <r>
     <x v="6"/>
     <x v="13"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3394,7 +3326,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="0"/>
-    <x v="63"/>
+    <n v="270"/>
     <n v="715"/>
     <n v="7"/>
     <n v="1"/>
@@ -3405,7 +3337,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3416,7 +3348,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3427,7 +3359,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3438,7 +3370,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="4"/>
-    <x v="7"/>
+    <n v="20"/>
     <n v="6"/>
     <n v="0"/>
     <n v="0"/>
@@ -3449,7 +3381,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3460,7 +3392,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="6"/>
-    <x v="22"/>
+    <n v="33"/>
     <n v="12"/>
     <n v="2"/>
     <n v="0"/>
@@ -3471,7 +3403,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3482,7 +3414,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="8"/>
-    <x v="21"/>
+    <n v="3"/>
     <n v="31"/>
     <n v="5"/>
     <n v="0"/>
@@ -3493,7 +3425,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3504,7 +3436,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="10"/>
-    <x v="31"/>
+    <n v="2"/>
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
@@ -3515,7 +3447,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="49"/>
     <n v="0"/>
@@ -3526,7 +3458,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3537,7 +3469,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="13"/>
-    <x v="14"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3548,7 +3480,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3559,7 +3491,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3570,7 +3502,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
@@ -3581,7 +3513,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -3592,7 +3524,7 @@
     <x v="6"/>
     <x v="14"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3603,7 +3535,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="0"/>
-    <x v="64"/>
+    <n v="519"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3614,7 +3546,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3625,7 +3557,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="21"/>
     <n v="0"/>
     <n v="0"/>
@@ -3636,7 +3568,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3647,7 +3579,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3658,7 +3590,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3669,7 +3601,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="137"/>
     <n v="0"/>
     <n v="0"/>
@@ -3680,7 +3612,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3691,7 +3623,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="7"/>
     <n v="0"/>
@@ -3702,7 +3634,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3713,7 +3645,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="45"/>
     <n v="0"/>
     <n v="1"/>
@@ -3724,7 +3656,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -3735,7 +3667,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3746,7 +3678,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="6"/>
     <n v="0"/>
     <n v="2"/>
@@ -3757,18 +3689,18 @@
     <x v="7"/>
     <x v="15"/>
     <x v="14"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="15"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3779,7 +3711,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3790,7 +3722,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -3801,7 +3733,7 @@
     <x v="7"/>
     <x v="15"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3812,7 +3744,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="0"/>
-    <x v="65"/>
+    <n v="737"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3823,7 +3755,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3834,7 +3766,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3845,7 +3777,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3856,7 +3788,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3867,18 +3799,18 @@
     <x v="7"/>
     <x v="16"/>
     <x v="5"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
   </r>
   <r>
     <x v="7"/>
     <x v="16"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3889,7 +3821,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3900,18 +3832,18 @@
     <x v="7"/>
     <x v="16"/>
     <x v="8"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="23"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="16"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3922,7 +3854,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3933,7 +3865,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3944,7 +3876,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3955,7 +3887,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3966,7 +3898,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3977,7 +3909,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3988,7 +3920,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3999,7 +3931,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -4010,7 +3942,7 @@
     <x v="7"/>
     <x v="16"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4021,7 +3953,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="0"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4032,7 +3964,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4043,7 +3975,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4054,7 +3986,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4065,7 +3997,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4076,7 +4008,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="5"/>
-    <x v="66"/>
+    <n v="100"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4087,18 +4019,18 @@
     <x v="7"/>
     <x v="17"/>
     <x v="6"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="45"/>
   </r>
   <r>
     <x v="7"/>
     <x v="17"/>
     <x v="7"/>
-    <x v="67"/>
+    <n v="1013"/>
     <n v="15"/>
     <n v="0"/>
     <n v="0"/>
@@ -4109,7 +4041,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="96"/>
     <n v="0"/>
@@ -4120,7 +4052,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4131,7 +4063,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4142,18 +4074,18 @@
     <x v="7"/>
     <x v="17"/>
     <x v="11"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="17"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4164,7 +4096,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4175,7 +4107,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4186,7 +4118,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4197,7 +4129,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4208,7 +4140,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4219,7 +4151,7 @@
     <x v="7"/>
     <x v="17"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4230,7 +4162,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="0"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4241,7 +4173,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4252,7 +4184,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4263,7 +4195,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4274,7 +4206,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4285,7 +4217,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4296,7 +4228,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4307,7 +4239,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4318,7 +4250,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="7"/>
     <n v="0"/>
     <n v="0"/>
@@ -4329,7 +4261,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4340,7 +4272,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4351,7 +4283,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4362,7 +4294,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4373,7 +4305,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4384,7 +4316,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4395,7 +4327,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4406,7 +4338,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
     <n v="0"/>
@@ -4417,7 +4349,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4428,7 +4360,7 @@
     <x v="7"/>
     <x v="18"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4439,7 +4371,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="0"/>
-    <x v="68"/>
+    <n v="346"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4450,20 +4382,20 @@
     <x v="7"/>
     <x v="19"/>
     <x v="1"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="19"/>
     <x v="2"/>
-    <x v="56"/>
+    <n v="25"/>
     <n v="2"/>
-    <n v="0"/>
+    <n v="2"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4472,18 +4404,18 @@
     <x v="7"/>
     <x v="19"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="41"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="55"/>
   </r>
   <r>
     <x v="7"/>
     <x v="19"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4494,7 +4426,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4505,7 +4437,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4516,7 +4448,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4527,7 +4459,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4538,7 +4470,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4549,7 +4481,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4560,7 +4492,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4571,7 +4503,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4582,7 +4514,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4593,7 +4525,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4604,7 +4536,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4615,7 +4547,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4626,7 +4558,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="20"/>
     <n v="0"/>
     <n v="0"/>
@@ -4637,7 +4569,7 @@
     <x v="7"/>
     <x v="19"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -4648,7 +4580,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="0"/>
-    <x v="69"/>
+    <n v="679"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4659,7 +4591,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4670,7 +4602,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4681,7 +4613,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4692,18 +4624,18 @@
     <x v="7"/>
     <x v="20"/>
     <x v="4"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
   </r>
   <r>
     <x v="7"/>
     <x v="20"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4714,7 +4646,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4725,7 +4657,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="7"/>
-    <x v="70"/>
+    <n v="279"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4736,7 +4668,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="8"/>
-    <x v="71"/>
+    <n v="4"/>
     <n v="42"/>
     <n v="0"/>
     <n v="0"/>
@@ -4747,7 +4679,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4758,7 +4690,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4769,7 +4701,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4780,7 +4712,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4791,7 +4723,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="4"/>
     <n v="0"/>
@@ -4802,7 +4734,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4813,7 +4745,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4824,7 +4756,7 @@
     <x v="7"/>
     <x v="20"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4835,18 +4767,18 @@
     <x v="7"/>
     <x v="20"/>
     <x v="17"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="20"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4857,7 +4789,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="0"/>
-    <x v="72"/>
+    <n v="421"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4868,7 +4800,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="1"/>
-    <x v="73"/>
+    <n v="964"/>
     <n v="11"/>
     <n v="7"/>
     <n v="2"/>
@@ -4879,7 +4811,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4890,7 +4822,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="28"/>
     <n v="0"/>
     <n v="0"/>
@@ -4901,7 +4833,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4912,18 +4844,18 @@
     <x v="7"/>
     <x v="21"/>
     <x v="5"/>
-    <x v="46"/>
+    <n v="6"/>
     <n v="3"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="34"/>
   </r>
   <r>
     <x v="7"/>
     <x v="21"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4934,20 +4866,20 @@
     <x v="7"/>
     <x v="21"/>
     <x v="7"/>
-    <x v="18"/>
+    <n v="45"/>
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <n v="3"/>
     <n v="0"/>
   </r>
   <r>
     <x v="7"/>
     <x v="21"/>
     <x v="8"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4956,7 +4888,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4967,7 +4899,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="10"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4978,7 +4910,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4989,7 +4921,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5000,7 +4932,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5011,7 +4943,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5022,9 +4954,9 @@
     <x v="7"/>
     <x v="21"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="14"/>
-    <n v="0"/>
+    <n v="3"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5033,18 +4965,18 @@
     <x v="7"/>
     <x v="21"/>
     <x v="16"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
   </r>
   <r>
     <x v="7"/>
     <x v="21"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5055,7 +4987,7 @@
     <x v="7"/>
     <x v="21"/>
     <x v="18"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5066,7 +4998,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="0"/>
-    <x v="74"/>
+    <n v="86"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5077,7 +5009,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5088,7 +5020,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="2"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5099,7 +5031,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5110,7 +5042,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="4"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5121,7 +5053,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="5"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5132,7 +5064,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5143,7 +5075,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="7"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5154,7 +5086,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="8"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5165,7 +5097,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="9"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5176,18 +5108,18 @@
     <x v="7"/>
     <x v="22"/>
     <x v="10"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="7"/>
     <x v="22"/>
     <x v="11"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5198,7 +5130,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="12"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5209,7 +5141,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="13"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5220,7 +5152,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="14"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5231,7 +5163,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="15"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5242,7 +5174,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="16"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5253,7 +5185,7 @@
     <x v="7"/>
     <x v="22"/>
     <x v="17"/>
-    <x v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5264,22 +5196,30 @@
     <x v="7"/>
     <x v="22"/>
     <x v="18"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DF7153E-FE7D-4B97-A70B-99A08C6E5571}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DF7153E-FE7D-4B97-A70B-99A08C6E5571}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G464" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" showAll="0">
-      <items count="9">
+      <items count="17">
+        <item m="1" x="8"/>
+        <item m="1" x="9"/>
+        <item m="1" x="10"/>
+        <item m="1" x="11"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -5343,86 +5283,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="76">
-        <item x="1"/>
-        <item x="54"/>
-        <item x="31"/>
-        <item x="21"/>
-        <item x="71"/>
-        <item x="14"/>
-        <item x="46"/>
-        <item x="11"/>
-        <item x="39"/>
-        <item x="47"/>
-        <item x="2"/>
-        <item x="41"/>
-        <item x="24"/>
-        <item x="40"/>
-        <item x="30"/>
-        <item x="7"/>
-        <item x="56"/>
-        <item x="49"/>
-        <item x="22"/>
-        <item x="15"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="10"/>
-        <item x="32"/>
-        <item x="25"/>
-        <item x="62"/>
-        <item x="6"/>
-        <item x="53"/>
-        <item x="74"/>
-        <item x="66"/>
-        <item x="58"/>
-        <item x="34"/>
-        <item x="43"/>
-        <item x="29"/>
-        <item x="16"/>
-        <item x="51"/>
-        <item x="9"/>
-        <item x="50"/>
-        <item x="27"/>
-        <item x="36"/>
-        <item x="61"/>
-        <item x="38"/>
-        <item x="35"/>
-        <item x="63"/>
-        <item x="70"/>
-        <item x="23"/>
-        <item x="48"/>
-        <item x="12"/>
-        <item x="68"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="52"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="45"/>
-        <item x="72"/>
-        <item x="44"/>
-        <item x="0"/>
-        <item x="64"/>
-        <item x="20"/>
-        <item x="69"/>
-        <item x="65"/>
-        <item x="17"/>
-        <item x="42"/>
-        <item x="73"/>
-        <item x="55"/>
-        <item x="67"/>
-        <item x="60"/>
-        <item x="33"/>
-        <item x="59"/>
-        <item x="37"/>
-        <item x="26"/>
-        <item x="28"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -20007,7 +19868,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -20145,7 +20006,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -20467,10 +20328,10 @@
         <v>4</v>
       </c>
       <c r="F24" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -20651,7 +20512,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -20700,7 +20561,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -21387,10 +21248,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="G64" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -21413,7 +21274,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -21479,7 +21340,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G68" s="3">
         <v>0</v>
@@ -21643,7 +21504,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -21847,10 +21708,10 @@
         <v>12</v>
       </c>
       <c r="F84" s="3">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G84" s="3">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -22057,7 +21918,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -22192,10 +22053,10 @@
         <v>0</v>
       </c>
       <c r="F99" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G99" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -22307,10 +22168,10 @@
         <v>100</v>
       </c>
       <c r="F104" s="3">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G104" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -22376,7 +22237,7 @@
         <v>3</v>
       </c>
       <c r="F107" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G107" s="3">
         <v>1</v>
@@ -22517,7 +22378,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -22767,10 +22628,10 @@
         <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G124" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -22882,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G129" s="3">
         <v>0</v>
@@ -23046,7 +22907,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -23227,10 +23088,10 @@
         <v>96</v>
       </c>
       <c r="F144" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G144" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -23437,7 +23298,7 @@
         <v>0</v>
       </c>
       <c r="G153" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -23621,7 +23482,7 @@
         <v>0</v>
       </c>
       <c r="G161" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -23641,7 +23502,7 @@
         <v>0</v>
       </c>
       <c r="F162" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G162" s="3">
         <v>0</v>
@@ -23687,7 +23548,7 @@
         <v>47</v>
       </c>
       <c r="F164" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G164" s="3">
         <v>2</v>
@@ -23825,7 +23686,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G170" s="3">
         <v>0</v>
@@ -24150,7 +24011,7 @@
         <v>2</v>
       </c>
       <c r="G184" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -24472,7 +24333,7 @@
         <v>1</v>
       </c>
       <c r="G198" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -24607,7 +24468,7 @@
         <v>1</v>
       </c>
       <c r="F204" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G204" s="3">
         <v>0</v>
@@ -24975,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G220" s="3">
         <v>0</v>
@@ -25061,16 +24922,16 @@
         <v>1</v>
       </c>
       <c r="D224" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E224" s="3">
         <v>31</v>
       </c>
       <c r="F224" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G224" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -25139,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -25360,13 +25221,13 @@
         <v>0</v>
       </c>
       <c r="D237" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E237" s="3">
         <v>0</v>
       </c>
       <c r="F237" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G237" s="3">
         <v>0</v>
@@ -25527,10 +25388,10 @@
         <v>0</v>
       </c>
       <c r="F244" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G244" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -25573,7 +25434,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G246" s="3">
         <v>0</v>
@@ -25829,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="G257" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -26441,16 +26302,16 @@
         <v>64</v>
       </c>
       <c r="D284" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E284" s="3">
         <v>0</v>
       </c>
       <c r="F284" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G284" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -26677,7 +26538,7 @@
         <v>0</v>
       </c>
       <c r="F294" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G294" s="3">
         <v>0</v>
@@ -26703,7 +26564,7 @@
         <v>0</v>
       </c>
       <c r="G295" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -26786,7 +26647,7 @@
         <v>2</v>
       </c>
       <c r="D299" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E299" s="3">
         <v>0</v>
@@ -26907,10 +26768,10 @@
         <v>0</v>
       </c>
       <c r="F304" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G304" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -26930,7 +26791,7 @@
         <v>0</v>
       </c>
       <c r="F305" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G305" s="3">
         <v>0</v>
@@ -27278,7 +27139,7 @@
         <v>0</v>
       </c>
       <c r="G320" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -27367,10 +27228,10 @@
         <v>6</v>
       </c>
       <c r="F324" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G324" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -27528,7 +27389,7 @@
         <v>0</v>
       </c>
       <c r="F331" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G331" s="3">
         <v>0</v>
@@ -27646,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -28287,10 +28148,10 @@
         <v>6</v>
       </c>
       <c r="F364" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G364" s="3">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -28471,7 +28332,7 @@
         <v>2</v>
       </c>
       <c r="F372" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G372" s="3">
         <v>0</v>
@@ -28497,7 +28358,7 @@
         <v>0</v>
       </c>
       <c r="G373" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -28586,7 +28447,7 @@
         <v>0</v>
       </c>
       <c r="F377" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G377" s="3">
         <v>0</v>
@@ -28635,7 +28496,7 @@
         <v>0</v>
       </c>
       <c r="G379" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -28741,16 +28602,16 @@
         <v>57</v>
       </c>
       <c r="D384" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E384" s="3">
         <v>2</v>
       </c>
       <c r="F384" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G384" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -28842,7 +28703,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -28856,7 +28717,7 @@
         <v>0</v>
       </c>
       <c r="D389" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E389" s="3">
         <v>0</v>
@@ -28954,7 +28815,7 @@
         <v>0</v>
       </c>
       <c r="F393" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G393" s="3">
         <v>0</v>
@@ -29026,7 +28887,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -29132,7 +28993,7 @@
         <v>14</v>
       </c>
       <c r="D401" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E401" s="3">
         <v>0</v>
@@ -29207,10 +29068,10 @@
         <v>4</v>
       </c>
       <c r="F404" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G404" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
@@ -29233,7 +29094,7 @@
         <v>0</v>
       </c>
       <c r="G405" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
@@ -29506,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="F417" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G417" s="3">
         <v>0</v>
@@ -29667,10 +29528,10 @@
         <v>0</v>
       </c>
       <c r="F424" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G424" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
@@ -30081,10 +29942,10 @@
         <v>0</v>
       </c>
       <c r="F442" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G442" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
@@ -30104,10 +29965,10 @@
         <v>0</v>
       </c>
       <c r="F443" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G443" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
@@ -30581,16 +30442,16 @@
         <v>8938</v>
       </c>
       <c r="D464" s="3">
-        <v>911</v>
+        <v>942</v>
       </c>
       <c r="E464" s="3">
         <v>381</v>
       </c>
       <c r="F464" s="3">
-        <v>115</v>
+        <v>398</v>
       </c>
       <c r="G464" s="3">
-        <v>49</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
